--- a/Team-Data/2013-14/4-3-2013-14.xlsx
+++ b/Team-Data/2013-14/4-3-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -769,7 +836,7 @@
         <v>2</v>
       </c>
       <c r="AN2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO2" t="n">
         <v>17</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-3-2013-14</t>
+          <t>2014-04-03</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>-4.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE3" t="n">
         <v>26</v>
@@ -981,7 +1048,7 @@
         <v>23</v>
       </c>
       <c r="AX3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY3" t="n">
         <v>13</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-3-2013-14</t>
+          <t>2014-04-03</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1227,7 @@
         <v>10</v>
       </c>
       <c r="AW4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX4" t="n">
         <v>28</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-3-2013-14</t>
+          <t>2014-04-03</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-0.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE5" t="n">
         <v>16</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-3-2013-14</t>
+          <t>2014-04-03</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>1.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE6" t="n">
         <v>12</v>
@@ -1527,7 +1594,7 @@
         <v>21</v>
       </c>
       <c r="AX6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY6" t="n">
         <v>28</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-3-2013-14</t>
+          <t>2014-04-03</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>-3.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE7" t="n">
         <v>22</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-3-2013-14</t>
+          <t>2014-04-03</t>
         </is>
       </c>
     </row>
@@ -1753,22 +1820,22 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E8" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F8" t="n">
         <v>31</v>
       </c>
       <c r="G8" t="n">
-        <v>0.592</v>
+        <v>0.587</v>
       </c>
       <c r="H8" t="n">
         <v>48.3</v>
       </c>
       <c r="I8" t="n">
-        <v>39.6</v>
+        <v>39.5</v>
       </c>
       <c r="J8" t="n">
         <v>83.59999999999999</v>
@@ -1777,13 +1844,13 @@
         <v>0.473</v>
       </c>
       <c r="L8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M8" t="n">
         <v>22.8</v>
       </c>
       <c r="N8" t="n">
-        <v>0.386</v>
+        <v>0.384</v>
       </c>
       <c r="O8" t="n">
         <v>17.3</v>
@@ -1792,16 +1859,16 @@
         <v>21.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.797</v>
+        <v>0.796</v>
       </c>
       <c r="R8" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="S8" t="n">
-        <v>30.6</v>
+        <v>30.5</v>
       </c>
       <c r="T8" t="n">
-        <v>40.8</v>
+        <v>40.7</v>
       </c>
       <c r="U8" t="n">
         <v>23.7</v>
@@ -1825,13 +1892,13 @@
         <v>20.1</v>
       </c>
       <c r="AB8" t="n">
-        <v>105.2</v>
+        <v>105.1</v>
       </c>
       <c r="AC8" t="n">
         <v>2.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AE8" t="n">
         <v>9</v>
@@ -1843,7 +1910,7 @@
         <v>9</v>
       </c>
       <c r="AH8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI8" t="n">
         <v>2</v>
@@ -1852,7 +1919,7 @@
         <v>11</v>
       </c>
       <c r="AK8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AL8" t="n">
         <v>8</v>
@@ -1888,7 +1955,7 @@
         <v>4</v>
       </c>
       <c r="AW8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AX8" t="n">
         <v>21</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-3-2013-14</t>
+          <t>2014-04-03</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>-2.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE9" t="n">
         <v>18</v>
@@ -2061,13 +2128,13 @@
         <v>7</v>
       </c>
       <c r="AT9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AU9" t="n">
         <v>12</v>
       </c>
       <c r="AV9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AW9" t="n">
         <v>17</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-3-2013-14</t>
+          <t>2014-04-03</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-3.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE10" t="n">
         <v>23</v>
@@ -2249,7 +2316,7 @@
         <v>21</v>
       </c>
       <c r="AV10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW10" t="n">
         <v>7</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-3-2013-14</t>
+          <t>2014-04-03</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>4.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE11" t="n">
         <v>8</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-3-2013-14</t>
+          <t>2014-04-03</t>
         </is>
       </c>
     </row>
@@ -2571,7 +2638,7 @@
         <v>6</v>
       </c>
       <c r="AH12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI12" t="n">
         <v>16</v>
@@ -2580,7 +2647,7 @@
         <v>28</v>
       </c>
       <c r="AK12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL12" t="n">
         <v>5</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-3-2013-14</t>
+          <t>2014-04-03</t>
         </is>
       </c>
     </row>
@@ -2741,13 +2808,13 @@
         <v>5</v>
       </c>
       <c r="AD13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE13" t="n">
         <v>4</v>
       </c>
       <c r="AF13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG13" t="n">
         <v>5</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-3-2013-14</t>
+          <t>2014-04-03</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E14" t="n">
         <v>54</v>
       </c>
       <c r="F14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G14" t="n">
-        <v>0.701</v>
+        <v>0.711</v>
       </c>
       <c r="H14" t="n">
         <v>48.2</v>
@@ -2863,28 +2930,28 @@
         <v>39</v>
       </c>
       <c r="J14" t="n">
-        <v>82.40000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="K14" t="n">
         <v>0.474</v>
       </c>
       <c r="L14" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="M14" t="n">
         <v>23.9</v>
       </c>
       <c r="N14" t="n">
-        <v>0.352</v>
+        <v>0.354</v>
       </c>
       <c r="O14" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="P14" t="n">
         <v>28.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.733</v>
+        <v>0.732</v>
       </c>
       <c r="R14" t="n">
         <v>10.5</v>
@@ -2899,7 +2966,7 @@
         <v>24.5</v>
       </c>
       <c r="V14" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="W14" t="n">
         <v>8.6</v>
@@ -2908,7 +2975,7 @@
         <v>4.8</v>
       </c>
       <c r="Y14" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Z14" t="n">
         <v>21.6</v>
@@ -2920,19 +2987,19 @@
         <v>107.7</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
       <c r="AD14" t="n">
         <v>1</v>
       </c>
       <c r="AE14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF14" t="n">
         <v>3</v>
       </c>
-      <c r="AF14" t="n">
-        <v>4</v>
-      </c>
       <c r="AG14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH14" t="n">
         <v>26</v>
@@ -2947,13 +3014,13 @@
         <v>3</v>
       </c>
       <c r="AL14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AM14" t="n">
         <v>8</v>
       </c>
       <c r="AN14" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AO14" t="n">
         <v>3</v>
@@ -2977,10 +3044,10 @@
         <v>3</v>
       </c>
       <c r="AV14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX14" t="n">
         <v>13</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-3-2013-14</t>
+          <t>2014-04-03</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-6.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE15" t="n">
         <v>25</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-3-2013-14</t>
+          <t>2014-04-03</t>
         </is>
       </c>
     </row>
@@ -3287,16 +3354,16 @@
         <v>1.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF16" t="n">
         <v>9</v>
       </c>
       <c r="AG16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH16" t="n">
         <v>20</v>
@@ -3317,7 +3384,7 @@
         <v>30</v>
       </c>
       <c r="AN16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO16" t="n">
         <v>30</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-3-2013-14</t>
+          <t>2014-04-03</t>
         </is>
       </c>
     </row>
@@ -3478,7 +3545,7 @@
         <v>3</v>
       </c>
       <c r="AG17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH17" t="n">
         <v>11</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-3-2013-14</t>
+          <t>2014-04-03</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-8.300000000000001</v>
       </c>
       <c r="AD18" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3681,7 +3748,7 @@
         <v>22</v>
       </c>
       <c r="AN18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO18" t="n">
         <v>22</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-3-2013-14</t>
+          <t>2014-04-03</t>
         </is>
       </c>
     </row>
@@ -3890,7 +3957,7 @@
         <v>6</v>
       </c>
       <c r="AW19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX19" t="n">
         <v>30</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-3-2013-14</t>
+          <t>2014-04-03</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>-2.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE20" t="n">
         <v>20</v>
@@ -4069,7 +4136,7 @@
         <v>18</v>
       </c>
       <c r="AV20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW20" t="n">
         <v>12</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-3-2013-14</t>
+          <t>2014-04-03</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-1.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE21" t="n">
         <v>18</v>
@@ -4233,7 +4300,7 @@
         <v>29</v>
       </c>
       <c r="AP21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ21" t="n">
         <v>17</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-3-2013-14</t>
+          <t>2014-04-03</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E22" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F22" t="n">
         <v>19</v>
       </c>
       <c r="G22" t="n">
-        <v>0.743</v>
+        <v>0.74</v>
       </c>
       <c r="H22" t="n">
         <v>48.3</v>
@@ -4328,7 +4395,7 @@
         <v>8.1</v>
       </c>
       <c r="M22" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="N22" t="n">
         <v>0.366</v>
@@ -4340,25 +4407,25 @@
         <v>24.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.805</v>
+        <v>0.804</v>
       </c>
       <c r="R22" t="n">
         <v>10.8</v>
       </c>
       <c r="S22" t="n">
-        <v>34.2</v>
+        <v>34.3</v>
       </c>
       <c r="T22" t="n">
-        <v>45</v>
+        <v>45.1</v>
       </c>
       <c r="U22" t="n">
         <v>21.9</v>
       </c>
       <c r="V22" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="W22" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X22" t="n">
         <v>6.1</v>
@@ -4367,19 +4434,19 @@
         <v>3.6</v>
       </c>
       <c r="Z22" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="AA22" t="n">
         <v>20.3</v>
       </c>
       <c r="AB22" t="n">
-        <v>106.1</v>
+        <v>106.2</v>
       </c>
       <c r="AC22" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="AD22" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -4403,13 +4470,13 @@
         <v>6</v>
       </c>
       <c r="AL22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AM22" t="n">
         <v>14</v>
       </c>
       <c r="AN22" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AO22" t="n">
         <v>5</v>
@@ -4427,16 +4494,16 @@
         <v>2</v>
       </c>
       <c r="AT22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AU22" t="n">
         <v>13</v>
       </c>
       <c r="AV22" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AW22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX22" t="n">
         <v>2</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-3-2013-14</t>
+          <t>2014-04-03</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>-5.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE23" t="n">
         <v>28</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-3-2013-14</t>
+          <t>2014-04-03</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-11.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE24" t="n">
         <v>29</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-3-2013-14</t>
+          <t>2014-04-03</t>
         </is>
       </c>
     </row>
@@ -4925,16 +4992,16 @@
         <v>2.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF25" t="n">
         <v>9</v>
       </c>
       <c r="AG25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH25" t="n">
         <v>24</v>
@@ -4982,7 +5049,7 @@
         <v>26</v>
       </c>
       <c r="AW25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX25" t="n">
         <v>17</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-3-2013-14</t>
+          <t>2014-04-03</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>4.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE26" t="n">
         <v>6</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-3-2013-14</t>
+          <t>2014-04-03</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-2.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE27" t="n">
         <v>23</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-3-2013-14</t>
+          <t>2014-04-03</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E28" t="n">
         <v>59</v>
       </c>
       <c r="F28" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G28" t="n">
-        <v>0.776</v>
+        <v>0.787</v>
       </c>
       <c r="H28" t="n">
         <v>48.2</v>
@@ -5411,10 +5478,10 @@
         <v>40.6</v>
       </c>
       <c r="J28" t="n">
-        <v>83.09999999999999</v>
+        <v>83</v>
       </c>
       <c r="K28" t="n">
-        <v>0.489</v>
+        <v>0.49</v>
       </c>
       <c r="L28" t="n">
         <v>8.4</v>
@@ -5423,13 +5490,13 @@
         <v>21.1</v>
       </c>
       <c r="N28" t="n">
-        <v>0.4</v>
+        <v>0.399</v>
       </c>
       <c r="O28" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="P28" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="Q28" t="n">
         <v>0.785</v>
@@ -5444,13 +5511,13 @@
         <v>43.3</v>
       </c>
       <c r="U28" t="n">
-        <v>25.3</v>
+        <v>25.4</v>
       </c>
       <c r="V28" t="n">
         <v>14.6</v>
       </c>
       <c r="W28" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X28" t="n">
         <v>5.2</v>
@@ -5465,13 +5532,13 @@
         <v>19.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>105.5</v>
+        <v>105.6</v>
       </c>
       <c r="AC28" t="n">
-        <v>8.300000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD28" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5483,7 +5550,7 @@
         <v>1</v>
       </c>
       <c r="AH28" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI28" t="n">
         <v>1</v>
@@ -5495,7 +5562,7 @@
         <v>2</v>
       </c>
       <c r="AL28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AM28" t="n">
         <v>17</v>
@@ -5525,13 +5592,13 @@
         <v>1</v>
       </c>
       <c r="AV28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW28" t="n">
         <v>19</v>
       </c>
       <c r="AX28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY28" t="n">
         <v>16</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-3-2013-14</t>
+          <t>2014-04-03</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>3.1</v>
       </c>
       <c r="AD29" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE29" t="n">
         <v>12</v>
@@ -5683,7 +5750,7 @@
         <v>11</v>
       </c>
       <c r="AN29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO29" t="n">
         <v>6</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-3-2013-14</t>
+          <t>2014-04-03</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>-7</v>
       </c>
       <c r="AD30" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE30" t="n">
         <v>26</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-3-2013-14</t>
+          <t>2014-04-03</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>0.9</v>
       </c>
       <c r="AD31" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE31" t="n">
         <v>15</v>
@@ -6041,7 +6108,7 @@
         <v>11</v>
       </c>
       <c r="AL31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AM31" t="n">
         <v>18</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-3-2013-14</t>
+          <t>2014-04-03</t>
         </is>
       </c>
     </row>
